--- a/test/session--empty-statements/reference/2 semester 14 subjects/рік/25-1/Відомості 25-1.xlsx
+++ b/test/session--empty-statements/reference/2 semester 14 subjects/рік/25-1/Відомості 25-1.xlsx
@@ -35,7 +35,7 @@
     <definedName name="Ф80" localSheetId="5">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Зведена J3'!$C$3:$S$20</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="F55" s="63">
-        <f>IF(F52="Очікую","Очікую",IF(F52-COUNTIF($T$10:$T46," - ")&lt;ROUNDDOWN(F52*0.4,0),F52-COUNTIF($T$10:$T46," - "),ROUNDDOWN(F52*0.4,0)))</f>
+        <f>IF(F52="Очікую","Очікую",IF(F52-COUNTIF($T$10:$T46," - ")&lt;ROUNDDOWN(F52*0.45,0),F52-COUNTIF($T$10:$T46," - "),ROUNDDOWN(F52*0.45,0)))</f>
         <v/>
       </c>
       <c r="G55" s="6" t="n"/>
@@ -3214,7 +3214,7 @@
       <c r="O55" s="54" t="n"/>
       <c r="P55" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q55" s="54" t="n"/>
@@ -3496,7 +3496,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності D5 ««Маркетинг»»</t>
+          <t>Успішності студентів спеціальності D5 «Маркетинг»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="F38" s="63">
-        <f>IF(F35="Очікую","Очікую",IF(F35-COUNTIF($T$10:$T29," - ")&lt;ROUNDDOWN(F35*0.4,0),F35-COUNTIF($T$10:$T29," - "),ROUNDDOWN(F35*0.4,0)))</f>
+        <f>IF(F35="Очікую","Очікую",IF(F35-COUNTIF($T$10:$T29," - ")&lt;ROUNDDOWN(F35*0.45,0),F35-COUNTIF($T$10:$T29," - "),ROUNDDOWN(F35*0.45,0)))</f>
         <v/>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -5627,7 +5627,7 @@
       <c r="O38" s="56" t="n"/>
       <c r="P38" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q38" s="54" t="n"/>
@@ -5930,7 +5930,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності E2 ««Екологія»»</t>
+          <t>Успішності студентів спеціальності E2 «Екологія»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="F31" s="63">
-        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($T$10:$T22," - ")&lt;ROUNDDOWN(F28*0.4,0),F28-COUNTIF($T$10:$T22," - "),ROUNDDOWN(F28*0.4,0)))</f>
+        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($T$10:$T22," - ")&lt;ROUNDDOWN(F28*0.45,0),F28-COUNTIF($T$10:$T22," - "),ROUNDDOWN(F28*0.45,0)))</f>
         <v/>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -7522,7 +7522,7 @@
       <c r="O31" s="56" t="n"/>
       <c r="P31" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q31" s="54" t="n"/>
@@ -7832,7 +7832,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G13 ««Харчові технології»»</t>
+          <t>Успішності студентів спеціальності G13 «Харчові технології»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="F19" s="63">
-        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($T$10:$T10," - ")&lt;ROUNDDOWN(F16*0.4,0),F16-COUNTIF($T$10:$T10," - "),ROUNDDOWN(F16*0.4,0)))</f>
+        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($T$10:$T10," - ")&lt;ROUNDDOWN(F16*0.45,0),F16-COUNTIF($T$10:$T10," - "),ROUNDDOWN(F16*0.45,0)))</f>
         <v/>
       </c>
       <c r="G19" s="6" t="n"/>
@@ -8500,7 +8500,7 @@
       <c r="O19" s="56" t="n"/>
       <c r="P19" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q19" s="54" t="n"/>
@@ -8822,7 +8822,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності J2 ««Готельно-ресторанна справа та кейтеринг»»</t>
+          <t>Успішності студентів спеціальності J2 «Готельно-ресторанна справа та кейтеринг»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="F19" s="63">
-        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($T$10:$T10," - ")&lt;ROUNDDOWN(F16*0.4,0),F16-COUNTIF($T$10:$T10," - "),ROUNDDOWN(F16*0.4,0)))</f>
+        <f>IF(F16="Очікую","Очікую",IF(F16-COUNTIF($T$10:$T10," - ")&lt;ROUNDDOWN(F16*0.45,0),F16-COUNTIF($T$10:$T10," - "),ROUNDDOWN(F16*0.45,0)))</f>
         <v/>
       </c>
       <c r="G19" s="6" t="n"/>
@@ -9490,7 +9490,7 @@
       <c r="O19" s="56" t="n"/>
       <c r="P19" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q19" s="54" t="n"/>
@@ -9812,7 +9812,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності J3 ««Туризм та рекреація»»</t>
+          <t>Успішності студентів спеціальності J3 «Туризм та рекреація»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -10539,7 +10539,7 @@
         </is>
       </c>
       <c r="F20" s="63">
-        <f>IF(F17="Очікую","Очікую",IF(F17-COUNTIF($T$10:$T11," - ")&lt;ROUNDDOWN(F17*0.4,0),F17-COUNTIF($T$10:$T11," - "),ROUNDDOWN(F17*0.4,0)))</f>
+        <f>IF(F17="Очікую","Очікую",IF(F17-COUNTIF($T$10:$T11," - ")&lt;ROUNDDOWN(F17*0.45,0),F17-COUNTIF($T$10:$T11," - "),ROUNDDOWN(F17*0.45,0)))</f>
         <v/>
       </c>
       <c r="G20" s="6" t="n"/>
@@ -10557,7 +10557,7 @@
       <c r="O20" s="56" t="n"/>
       <c r="P20" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q20" s="54" t="n"/>
